--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -21036,7 +21036,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>il quale difatti, già in ansimo, annunciava il lùbrico gioco de' manovellismi su su su fu fu fu da 'e Fattocchie, vincendo la implorazione lontana der cuccù.</t>
+          <t>il quale difatti, già in ansimo, annunciava il lùbrico gioco de' manovellismi su su su fu fu fu da 'e Frattocchie, vincendo la implorazione lontana der cuccù.</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H723"/>
+  <dimension ref="A1:H724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25730,6 +25730,41 @@
         </is>
       </c>
     </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>ref_00723</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>casal_bruciato</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>capitolo_IX</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>quer_pasticciaccio_adelphi</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>A 241</t>
+        </is>
+      </c>
+      <c r="F724" t="n">
+        <v>241</v>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>Al casello, detto da taluni di Casal Bruciato, lo si attendeva ogni giorno, una volta al giorno.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H724"/>
+  <dimension ref="A1:I728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>Excerpt</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Witness_ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25762,6 +25767,148 @@
       <c r="H724" t="inlineStr">
         <is>
           <t>Al casello, detto da taluni di Casal Bruciato, lo si attendeva ogni giorno, una volta al giorno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>ref_00724</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>frattocchie</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>quer_pasticciaccio</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>RR II 219</t>
+        </is>
+      </c>
+      <c r="F725" t="n">
+        <v>219</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Lezione della stampa Garzanti, emendata dall'editore in QP 241 (variante V-0001).</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>su su su fu fu fu da 'e Fattocchie</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>rr2</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>ref_00725</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>via_lanza</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>quer_pasticciaccio</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>dtsFG</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Il dattiloscritto dei capitoli nuovi legge «via Lata» dove QP 177 legge «via Lanza» (Pinotti 2025, p. 78; variante V-0002). Pagina del dattiloscritto non registrata.</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>dtsfg</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>ref_00726</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>palazzo_219</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>quer_pasticciaccio</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>QPL 285</t>
+        </is>
+      </c>
+      <c r="F727" t="n">
+        <v>285</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Redazione di «Letteratura»: civico 119 e «palazzo degli ori» (varianti V-0003, V-0004). Citata da RR II.</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>qpl</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>ref_00727</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>palazzo_219</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>quer_pasticciaccio</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>QPL 293</t>
+        </is>
+      </c>
+      <c r="F728" t="n">
+        <v>293</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Redazione di «Letteratura»: civico 119 e «palazzo degli ori» (varianti V-0003, V-0004). Citata da RR II.</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>qpl</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H728"/>
+  <dimension ref="A1:I728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>Witness_ID</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Attested_Form</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -702,6 +707,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>palazzo der ducentodicinnove</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -737,6 +747,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>er palazzo dell’oro</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -842,6 +857,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>frascatano</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1157,6 +1177,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Santi Quattro</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1192,6 +1217,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Porta Paradisi</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1402,6 +1432,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>palazzo dell’Oro</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1507,6 +1542,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ducentodicinnove</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1577,6 +1617,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Botteghe Oscure</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1717,6 +1762,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>civico ducentodicinnove</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1787,6 +1837,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>palazzo dell’Oro</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1822,6 +1877,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ben nota architettura</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1857,6 +1917,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>casermone color pidocchio</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1892,6 +1957,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sto palazzo</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1997,6 +2067,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sacro Core</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2067,6 +2142,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ducentodiciannove</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2137,6 +2217,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>La A</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2312,6 +2397,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Tranvie de li Castelli</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2487,6 +2577,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Santi Quattro</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2697,6 +2792,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>la Scrofa</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2732,6 +2832,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>via de le Coppelle</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2767,6 +2872,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Pozzo de le Cornacchie</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2872,6 +2982,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>via Colonna</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2907,6 +3022,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>piazza de Pietra</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2942,6 +3062,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>via de Pietra</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3012,6 +3137,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Enciclopedia Treccani</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3152,6 +3282,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Palommella</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3187,6 +3322,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Panteone</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3257,6 +3397,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Campo Marzio</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3362,6 +3507,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>ducentodicinnove</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3467,6 +3617,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>via der Gesù</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3502,6 +3657,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Santo Stefano der Cacco</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3642,6 +3802,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>de li Serpenti</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3677,6 +3842,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>li Serpenti</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3852,6 +4022,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>palazzo dell’Oro</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3957,6 +4132,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>San Giovanni</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4062,6 +4242,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>la B</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4132,6 +4317,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Sant’Antonio de Padova</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4167,6 +4357,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Santi Quattro</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4202,6 +4397,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Labbicana</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4307,6 +4507,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>San Lorenzo in Lucina</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4377,6 +4582,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>San Silvestro</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4832,6 +5042,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>grotta der sor Pippo</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5182,6 +5397,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Giannicolo</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5217,6 +5437,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Colleggio Romano</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5497,6 +5722,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Faiti</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5602,6 +5832,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Forte de marmo</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5742,6 +5977,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Sacro Core</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5777,6 +6017,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5882,6 +6127,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Sacro Core</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6127,6 +6377,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>via de li Banchi Vecchi</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6197,6 +6452,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6302,6 +6562,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Tranvie de li Castelli</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6442,6 +6707,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>via Panesperna</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6722,6 +6992,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>piazza Vittorio</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6757,6 +7032,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Palazzo Chiggi</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7037,6 +7317,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>cantina di Albano</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7142,6 +7427,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>via Frangipani</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7177,6 +7467,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>li Zingari</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7212,6 +7507,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>via de li Capocci</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7317,6 +7617,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>via de Monte Caprino</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7352,6 +7657,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>vicolo de la Bucimazza</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7387,6 +7697,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>via de’ Fienili</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7457,6 +7772,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Sant’Andrea de la Valle</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7492,6 +7812,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Grotta Pinta</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7562,6 +7887,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>vicolo de le Grotte der Teatro</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7737,6 +8067,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>ducentodiciannove</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7912,6 +8247,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8227,6 +8567,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>palazzo Chiggi</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8297,6 +8642,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Banca Commerciale</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8332,6 +8682,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Banco de Santo Spirito</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8402,6 +8757,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Santi Quattro</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8437,6 +8797,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>palazzo Chiggi</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8612,6 +8977,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>piazza Vittorio</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8682,6 +9052,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Banco de Santo Spirito</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8892,6 +9267,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Santi Quattro</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8927,6 +9307,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>palazzo del ducentodicinnove</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8962,6 +9347,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Prati</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8997,6 +9387,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>villino a lungotevere</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9872,6 +10267,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>palazzo Chigge</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10187,6 +10587,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>San Lorenzo in Lucina</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10397,6 +10802,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>de li Banchi Vecchi</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10432,6 +10842,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Banco de Santo Spirito</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10677,6 +11092,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>piazza Vittorio</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10712,6 +11132,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Soriano ar Cimìno</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10747,6 +11172,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>San Giovanni</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10817,6 +11247,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10852,6 +11287,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Sacro Core</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10887,6 +11327,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>de li Banchi Vecchi</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11062,6 +11507,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>San Lorenzo ar Verano</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11657,6 +12107,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Santi Quattro</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11832,6 +12287,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Sacro Core</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11937,6 +12397,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>San Giovanni Laterano</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12392,6 +12857,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Toraccio</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12427,6 +12897,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>via Orà-zio</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12777,6 +13252,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>via der Gesù</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -13547,6 +14027,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>piazza Vittorio</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13722,6 +14207,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13792,6 +14282,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Santo Stefano del Cacco</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13932,6 +14427,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -14037,6 +14537,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -14247,6 +14752,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>laboratorio della Zamira</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -14352,6 +14862,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>l'Ardeatina</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14387,6 +14902,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>l'Anziate</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -14632,6 +15152,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Divino Amore</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -14702,6 +15227,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -14737,6 +15267,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -14912,6 +15447,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Castel Savelli</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -15262,6 +15802,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>l'Ardeatina</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -15297,6 +15842,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Anziate</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -15612,6 +16162,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Palomba</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15787,6 +16342,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>carabinieri di Marino</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -15822,6 +16382,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>via der Gesù</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -15997,6 +16562,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>strada de campagna</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -16102,6 +16672,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Santo Stefano Rotondo</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -16207,6 +16782,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Tempio d’Agrippa</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -16277,6 +16857,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -16382,6 +16967,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>trasteverino</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -16767,6 +17357,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>pensione Bergèss</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -16802,6 +17397,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Pensione Bergesse</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -17082,6 +17682,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Reggio (Calabria)</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -17257,6 +17862,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -17327,6 +17937,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>piazza Vittorio</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -17397,6 +18012,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>San Giovanni</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -17502,6 +18122,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>funtanella de Borghese</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -17747,6 +18372,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Buco a Sant’Ignazzio</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -17782,6 +18412,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Villa Porchese</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -18097,6 +18732,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>piazza Vittorio</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -18167,6 +18807,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>piazza Vittorio</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -18237,6 +18882,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>bottega</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -18517,6 +19167,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>porta del borgo</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -18622,6 +19277,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Carseolani</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -18832,6 +19492,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Velino</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -18937,6 +19602,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Ladìspoli</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -19112,6 +19782,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -19217,6 +19892,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Campo Morto</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -19252,6 +19932,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>monte della contessa Circia</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -19322,6 +20007,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Castel Porcino</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -19357,6 +20047,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -19427,6 +20122,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Simbruini</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -19604,6 +20304,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>botteguccia</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -19779,6 +20484,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -19814,6 +20524,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>edicola delli Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -19989,6 +20704,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>bottega</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -20199,6 +20919,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -20269,6 +20994,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Castel de Leva</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -20409,6 +21139,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Divino Amore</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -20444,6 +21179,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>ponte del Divino Amore</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -20479,6 +21219,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>ponte del Divino Amore</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -20619,6 +21364,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Falcognana</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -20829,6 +21579,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Falcognana</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -20864,6 +21619,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>ponte del Divino Amore</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -20969,6 +21729,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>casello chilometro 20,25</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -21249,6 +22014,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>ponte (del Divino Amore)</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -21319,6 +22089,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>bottega</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -21844,6 +22619,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>chilometro 20,25</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -22159,6 +22939,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>li Du Santi</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -22369,6 +23154,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Santa Rita in Vitàcolo</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -22439,6 +23229,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Castelli</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -22509,6 +23304,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>anziate</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -22614,6 +23414,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>l'ardeatina</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -22894,6 +23699,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>anziate</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -23454,6 +24264,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>piazza Vittorio</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -23769,6 +24584,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Caffarella</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -23979,6 +24799,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Piazza Vittorio Manuele</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -24014,6 +24839,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>piazza de Spagna</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -24294,6 +25124,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Merulana</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -24399,6 +25234,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>via Massimo Dazzélio</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -24784,6 +25624,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Casale Abbrusciato</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -24819,6 +25664,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>ferrovia di Velletri</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -24854,6 +25704,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>ponte del Divino Amore</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -25029,6 +25884,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>stazzione</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -25099,6 +25959,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Tor der Gheppio</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -25204,6 +26069,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>l’ardeatina</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -25379,6 +26249,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Pratica de Mare</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -25589,6 +26464,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Crocchiapani</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -25624,6 +26504,11 @@
           <t>qp</t>
         </is>
       </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Tor de Gheppio</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -25799,6 +26684,11 @@
           <t>rr2</t>
         </is>
       </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>Fattocchie</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -25824,6 +26714,11 @@
       <c r="H726" t="inlineStr">
         <is>
           <t>dtsfg</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>via Lata</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I728"/>
+  <dimension ref="A1:I730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -26779,6 +26779,76 @@
       <c r="H728" t="inlineStr">
         <is>
           <t>qpl</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>ref_00728</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>tragitto_sogno_casal_bruciato_campo_morto</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>capitolo_VIII</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>A 212</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>212</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>Tantoché al passaggio a livello di Casal Bruciato il vetrone girasole... per fil a dest! […] E il Roma-Napoli filava filava a tutta corsa dietro al crepuscolo e pressoché già nella notte e nella tenebra circèa. […] S’era buttato alla campagna nella notte verso le gore senza foce del Campo Morto e la macchia e l’intrico del litorale pometino.</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>qp</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>ref_00729</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>tragitto_castel_di_leva_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>capitolo_VIII</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>A 237</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>237</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>« Quale passaggio? » « Pe la strada de Castel de Leva, fino ar ponte: poi, a sinistra, fino ar passaggio a livello de Casal Bruciato. »</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>qp</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -6017,11 +6017,6 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6452,11 +6447,6 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8247,11 +8237,6 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11247,11 +11232,6 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15227,11 +15207,6 @@
           <t>qp</t>
         </is>
       </c>
-      <c r="I408" t="inlineStr">
-        <is>
-          <t>Milano</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -15265,11 +15240,6 @@
       <c r="H409" t="inlineStr">
         <is>
           <t>qp</t>
-        </is>
-      </c>
-      <c r="I409" t="inlineStr">
-        <is>
-          <t>Milano</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I730"/>
+  <dimension ref="A1:I731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10317,6 +10317,11 @@
       <c r="E272" t="n">
         <v>116</v>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Prima menzione di via Nicotera a QP 116; la seconda e' ref_00730 (D-072).</t>
+        </is>
+      </c>
       <c r="G272" t="inlineStr">
         <is>
           <t>il Valdarena: che abitava in Prati, in una bella camera-studio a via Nicotera: un villino […].</t>
@@ -26817,6 +26822,46 @@
         </is>
       </c>
       <c r="H730" t="inlineStr">
+        <is>
+          <t>qp</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>ref_00730</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>via_nicotera</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>capitolo_IV</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>A 116</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>116</v>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Seconda menzione di via Nicotera a QP 116, separata da ref_00271 (D-072). Estratto fornito da LS.</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Sul marmo del cassettone, a via Nicotera, "fu rinvenuto"…</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
         <is>
           <t>qp</t>
         </is>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8924,7 +8924,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Prima menzione di via Nicotera a QP 116; la seconda e' ref_00730 (D-072).</t>
+          <t>Prima menzione di via Nicotera a QPa 116; la seconda e' ref_00730 (D-072).</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12524,7 +12524,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13344,7 +13344,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13589,7 +13589,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13624,7 +13624,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14154,7 +14154,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14844,7 +14844,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15349,7 +15349,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15669,7 +15669,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16099,7 +16099,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16244,7 +16244,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16279,7 +16279,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16314,7 +16314,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16719,7 +16719,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17014,7 +17014,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17119,7 +17119,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17329,7 +17329,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -17369,7 +17369,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17479,7 +17479,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17514,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17549,7 +17549,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18204,7 +18204,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -18384,7 +18384,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18494,7 +18494,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18529,7 +18529,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18599,7 +18599,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18779,7 +18779,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19069,7 +19069,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19104,7 +19104,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19139,7 +19139,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19324,7 +19324,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19394,7 +19394,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19464,7 +19464,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19754,7 +19754,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20171,7 +20171,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20206,7 +20206,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20351,7 +20351,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20386,7 +20386,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20571,7 +20571,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20606,7 +20606,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20641,7 +20641,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20676,7 +20676,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20786,7 +20786,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20821,7 +20821,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20891,7 +20891,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21481,7 +21481,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21516,7 +21516,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21551,7 +21551,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -21591,7 +21591,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -21631,7 +21631,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -21741,7 +21741,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21776,7 +21776,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21811,7 +21811,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21846,7 +21846,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21916,7 +21916,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -21986,7 +21986,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22136,7 +22136,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22171,7 +22171,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22206,7 +22206,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22276,7 +22276,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22311,7 +22311,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22346,7 +22346,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22486,7 +22486,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22556,7 +22556,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22736,7 +22736,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22771,7 +22771,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22806,7 +22806,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -22986,7 +22986,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23056,7 +23056,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23276,7 +23276,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23351,7 +23351,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23386,7 +23386,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23461,7 +23461,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23496,7 +23496,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23531,7 +23531,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23566,7 +23566,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23601,7 +23601,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23636,7 +23636,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23671,7 +23671,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23746,7 +23746,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23781,7 +23781,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23816,7 +23816,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23886,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23921,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23956,7 +23956,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -23991,7 +23991,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24026,7 +24026,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24061,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24131,7 +24131,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24166,7 +24166,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24236,7 +24236,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24416,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24451,7 +24451,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24486,7 +24486,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24521,7 +24521,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24556,7 +24556,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24666,7 +24666,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24701,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24736,7 +24736,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -24851,7 +24851,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24921,7 +24921,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25026,7 +25026,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25061,7 +25061,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25096,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25171,7 +25171,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25206,7 +25206,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -25246,7 +25246,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25316,7 +25316,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25351,7 +25351,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25386,7 +25386,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25421,7 +25421,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25491,7 +25491,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -25636,7 +25636,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -25716,7 +25716,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25786,7 +25786,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25856,7 +25856,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -25896,7 +25896,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26041,7 +26041,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -26081,7 +26081,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26151,7 +26151,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26186,7 +26186,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26221,7 +26221,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -26261,7 +26261,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26296,7 +26296,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26366,7 +26366,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26401,7 +26401,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26436,7 +26436,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -26476,7 +26476,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26621,7 +26621,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26638,7 +26638,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>RR II 219</t>
+          <t>QP 219 (RR II)</t>
         </is>
       </c>
       <c r="E725" t="n">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>Lezione della stampa Garzanti, emendata dall'editore in QP 241 (variante V-0001).</t>
+          <t>Lezione della versione in volume (QP), letta in RR II, p. 219; emendata dall'editore in QPa 241 (variante V-0001).</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -26656,7 +26656,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>rr2</t>
+          <t>qp</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -26683,7 +26683,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Il dattiloscritto dei capitoli nuovi legge «via Lata» dove QP 177 legge «via Lanza» (Pinotti 2025, p. 78; variante V-0002). Pagina del dattiloscritto non registrata.</t>
+          <t>Il dattiloscritto dei capitoli nuovi legge «via Lata» dove QPa 177 legge «via Lanza» (Pinotti 2025, p. 78; variante V-0002). Pagina del dattiloscritto non registrata.</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>Seconda menzione di via Nicotera a QP 116, separata da ref_00271 (D-072). Estratto fornito da LS.</t>
+          <t>Seconda menzione di via Nicotera a QPa 116, separata da ref_00271 (D-072). Estratto fornito da LS.</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -26863,7 +26863,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>qp</t>
+          <t>qpa</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I731"/>
+  <dimension ref="A1:I734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5967,9 +5967,14 @@
       <c r="E152" t="n">
         <v>65</v>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Prima menzione della pagina; la seconda e' un'occorrenza distinta (D-075). Estratto da verificare sul volume a stampa.</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Riferirono ad Ingravallo che la Gina, la pupilla, era tornata dar Sacro Core, in quer momento. Il giovedì rientrava all’una: per la colazione. [...] Sì, un po’ prima della Gina, che annava ar Sacro Core alle otto. Non volle sostare a quella vista: «Nun me riesce de guardalla.» Se fece er segno de la croce.</t>
+          <t>Riferirono ad Ingravallo che la Gina, la pupilla, era tornata dar Sacro Core, in quer momento.</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6902,9 +6907,14 @@
       <c r="E178" t="n">
         <v>76</v>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Prima menzione della pagina; la seconda e' un'occorrenza distinta (D-075). Estratto da verificare sul volume a stampa.</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>La mattina dopo i giornali diedero notizia del fatto. Era venerdì. Li cronisti e il telefono aveveno rotto l’anima tutta la sera: tanto a via Merulana che giù, a Sante Stefene. Sicché, la mattina, un subisso. «Orribile delitto a via Merulana,» gridavano li strilloni, co li pacchi fra li ginocchi de la gente: fino all’undici e tre quarti.</t>
+          <t>Li cronisti e il telefono aveveno rotto l’anima tutta la sera: tanto a via Merulana che giù, a Sante Stefene.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -9242,9 +9252,14 @@
       <c r="E242" t="n">
         <v>105</v>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Prima menzione della pagina; la seconda e' un'occorrenza distinta (D-075). Estratto da verificare sul volume a stampa.</t>
+        </is>
+      </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>E quella malinconia di Liliana. Quella specie di fissazione. E poi co li Santi Quattro là vicino. «Che Liliana, Madonna! guai a sentimme dì de portalla via da li Santi Quattro!»</t>
+          <t>E poi co li Santi Quattro là vicino.</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -26864,6 +26879,136 @@
       <c r="H731" t="inlineStr">
         <is>
           <t>qpa</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>ref_00731</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>sacro_cuore</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>capitolo_II</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>A 65</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>65</v>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Seconda menzione della pagina, separata da ref_00151 (D-075). Estratto da verificare sul volume a stampa.</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>Sì, un po’ prima della Gina, che annava ar Sacro Core alle otto.</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Sacro Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>ref_00732</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>via_merulana</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>capitolo_III</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>A 76</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>76</v>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Seconda menzione della pagina, separata da ref_00177 (D-075). Estratto da verificare sul volume a stampa.</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>«Orribile delitto a via Merulana,» gridavano li strilloni, co li pacchi fra li ginocchi de la gente: fino all’undici e tre quarti.</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>ref_00733</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>santi_quattro_coronati</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>capitolo_IV</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>A 105</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>105</v>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Seconda menzione della pagina, separata da ref_00241 (D-075). Estratto da verificare sul volume a stampa.</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>«Che Liliana, Madonna! guai a sentimme dì de portalla via da li Santi Quattro!»</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Santi Quattro</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I734"/>
+  <dimension ref="A1:I737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27012,6 +27012,103 @@
         </is>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>ref_00734</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>marino</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>QPL 324 (RR II)</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>324</v>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Redazione di «Letteratura»: «Marino», sostituito in QPa 56 dalle fermate del tram (Due Santi, Torraccio, Frattocchie): variante di sostituzione V-0005 (Terzoli 2015, p. 142; D-087). Estratto non registrato.</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>qpl</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>ref_00735</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>dtsFG</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Il dattiloscritto dei capitoli nuovi legge «da Faraja» dove QPa 200 legge «a la Vite»: variante di sostituzione V-0006 (Pinotti 2025, p. 78). Nessun luogo: l'identificazione con il Gran Caffè Faraglia sta nella lettura di Pinotti (D-087).</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>dtsfg</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>ref_00736</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>osteriuccia_bivio</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>capitolo_IX</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>A 239</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>239</v>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Estratto fornito da LS (D-087).</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Imbarcati i due sposi, lui ritornò addietro verso l’osteriuccia del bivio, a chiedere una bicicletta da quarcuno: e se no sarebbe risalito fino dalla Zamira, a recuperare la cavalla.</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>osteriuccia del bivio</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I737"/>
+  <dimension ref="A1:I745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27109,6 +27109,366 @@
         </is>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>ref_00737</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>capitolo_VI</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>A 165</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>165</v>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Estratto verificato da LS sul volume a stampa (D-091).</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>La cantina, o sala seminterrata, era provveduta d’un orinale: e, più, d’un lettuccio: che però crocchiava per un nulla, sto coglione, e aveva tegumento d’una « coperta da letto » verde-stinta</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>cantina</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>ref_00738</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>capitolo_VI</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>A 165</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>165</v>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Estratto verificato da LS sul volume a stampa (D-091).</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Dava adito, codesto salotto o sala di consultazione, per uscio con catenaccio, al sacello o ricettacolo responsale propriamente detto.</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>salotto o sala di consultazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>ref_00739</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>sacello_responsale</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>capitolo_VI</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>A 165</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>165</v>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Estratto verificato da LS sul volume a stampa (D-091).</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>Dava adito, codesto salotto o sala di consultazione, per uscio con catenaccio, al sacello o ricettacolo responsale propriamente detto.</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>sacello o ricettacolo responsale</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>ref_00740</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>capitolo_VI</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>A 166</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>166</v>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Estratto verificato da LS sul volume a stampa (D-091).</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Un punto d’incontro dei vitali compossibili: magia, maglieria, sartoria, pantaloneria, vino de li Castelli e de Bitonto pure (una botte, la spina: due damigiane, li sifoni de gomma), cacio e fave, d’aprile, il nipotino del duce dei baffoni a ruzzare per entro il teschio, in cantina, cioè nella « sala di tintoria »</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>cantina</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>ref_00741</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>capitolo_VI</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>A 169</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>169</v>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Estratto verificato da LS sul volume a stampa (D-091).</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>La Zamira lo mandò a levarseli in cantina: e gli mandò dietro la Clelia, o, secondo altri, la Camilla, per prendere i pantaloni e portarli su a raccomodare, in laboratorio.</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>cantina</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>ref_00742</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>capitolo_VII</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>A 195</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>195</v>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Estratto verificato da LS sul volume a stampa (D-091).</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>E lui je taceva puro da confidente, allora. E certe vorte nun te l’attirò puro in cantina, pe parlaje co più commodo! Me sa che je dicesse quarche cosa d’importante. Svergognata! a l’età sua!</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>cantina</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>ref_00743</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>capitolo_VII</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>A 196</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>196</v>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Estratto verificato da LS sul volume a stampa (D-091).</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>Ines non proferì per esplicito, ma sembrò loro di poter tuttavia desumere dall’apprezzato raccontino della discesa in antro (del biondo intraprendente con la più che Cumana Sibilla)</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>antro</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>ref_00744</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>camera_sicurezza_questura</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>capitolo_VII</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>A 176</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>176</v>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Estratto verificato da LS sul volume a stampa (D-091).</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Povera figliola, avrebbe atteso l’alba sul tavolaccio della camera di sicurezza, rinvoltata dentro una copertuccia bigia da caserma all’insegna der pidocchietto</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>qpa</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>camera di sicurezza</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/References.xlsx
+++ b/data/source/xlsx/References.xlsx
@@ -27275,7 +27275,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>Un punto d’incontro dei vitali compossibili: magia, maglieria, sartoria, pantaloneria, vino de li Castelli e de Bitonto pure (una botte, la spina: due damigiane, li sifoni de gomma), cacio e fave, d’aprile, il nipotino del duce dei baffoni a ruzzare per entro il teschio, in cantina, cioè nella « sala di tintoria »</t>
+          <t>il nipotino del duce dei baffoni a ruzzare per entro il teschio, in cantina, cioè nella « sala di tintoria »</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
